--- a/artfynd/A 63684-2020 artfynd.xlsx
+++ b/artfynd/A 63684-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120284986</v>
       </c>
       <c r="B2" t="n">
-        <v>79542</v>
+        <v>79558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120285005</v>
+        <v>120285251</v>
       </c>
       <c r="B3" t="n">
-        <v>91182</v>
+        <v>102240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,38 +818,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>223246</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -857,10 +858,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538478</v>
+        <v>538473</v>
       </c>
       <c r="R3" t="n">
-        <v>6647653</v>
+        <v>6647623</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,6 +894,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca 7 cm i diameter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,26 +914,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # vilande på grenarna # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120285251</v>
+        <v>120285005</v>
       </c>
       <c r="B4" t="n">
-        <v>102217</v>
+        <v>91200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,39 +943,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223246</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -997,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538473</v>
+        <v>538478</v>
       </c>
       <c r="R4" t="n">
-        <v>6647623</v>
+        <v>6647653</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1033,11 +1018,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ca 7 cm i diameter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,6 +1033,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # vilande på grenarna # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 63684-2020 artfynd.xlsx
+++ b/artfynd/A 63684-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120284986</v>
+        <v>120285251</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
+        <v>102240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6457</v>
+        <v>223246</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538478</v>
+        <v>538473</v>
       </c>
       <c r="R2" t="n">
-        <v>6647653</v>
+        <v>6647623</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ca 7 cm i diameter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,26 +783,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>grovt träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Acer platanoides # grovt träd</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120285251</v>
+        <v>120284986</v>
       </c>
       <c r="B3" t="n">
-        <v>102240</v>
+        <v>79558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,39 +812,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>6457</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -858,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538473</v>
+        <v>538478</v>
       </c>
       <c r="R3" t="n">
-        <v>6647623</v>
+        <v>6647653</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,11 +879,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca 7 cm i diameter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,6 +894,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Acer platanoides # grovt träd</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 63684-2020 artfynd.xlsx
+++ b/artfynd/A 63684-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120285251</v>
+        <v>120284986</v>
       </c>
       <c r="B2" t="n">
-        <v>102240</v>
+        <v>79558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>6457</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538473</v>
+        <v>538478</v>
       </c>
       <c r="R2" t="n">
-        <v>6647623</v>
+        <v>6647653</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ca 7 cm i diameter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,6 +769,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Acer platanoides # grovt träd</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120284986</v>
+        <v>120285005</v>
       </c>
       <c r="B3" t="n">
-        <v>79558</v>
+        <v>91200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,25 +822,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -898,22 +912,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>grovt träd</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Acer platanoides # grovt träd</t>
+          <t>Horizontal, dead without ground contact # vilande på grenarna # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -931,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120285005</v>
+        <v>120285251</v>
       </c>
       <c r="B4" t="n">
-        <v>91200</v>
+        <v>102240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,38 +957,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>223246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -982,10 +997,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538478</v>
+        <v>538473</v>
       </c>
       <c r="R4" t="n">
-        <v>6647653</v>
+        <v>6647623</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1018,6 +1033,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ca 7 cm i diameter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,26 +1053,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # vilande på grenarna # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 63684-2020 artfynd.xlsx
+++ b/artfynd/A 63684-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120284986</v>
+        <v>120285005</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
+        <v>91200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,25 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -773,22 +781,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>grovt träd</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Acer platanoides # grovt träd</t>
+          <t>Horizontal, dead without ground contact # vilande på grenarna # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120285005</v>
+        <v>120285251</v>
       </c>
       <c r="B3" t="n">
-        <v>91200</v>
+        <v>102240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,38 +826,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>223246</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -857,10 +866,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538478</v>
+        <v>538473</v>
       </c>
       <c r="R3" t="n">
-        <v>6647653</v>
+        <v>6647623</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,6 +902,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca 7 cm i diameter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,26 +922,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # vilande på grenarna # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120285251</v>
+        <v>120284986</v>
       </c>
       <c r="B4" t="n">
-        <v>102240</v>
+        <v>79558</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,39 +951,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223246</v>
+        <v>6457</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -997,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538473</v>
+        <v>538478</v>
       </c>
       <c r="R4" t="n">
-        <v>6647623</v>
+        <v>6647653</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1033,11 +1018,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ca 7 cm i diameter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,6 +1033,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Acer platanoides # grovt träd</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 63684-2020 artfynd.xlsx
+++ b/artfynd/A 63684-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120285005</v>
+        <v>120284986</v>
       </c>
       <c r="B2" t="n">
-        <v>91200</v>
+        <v>79558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -781,22 +773,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # vilande på grenarna # Picea abies</t>
+          <t>Acer platanoides # grovt träd</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120285251</v>
+        <v>120285005</v>
       </c>
       <c r="B3" t="n">
-        <v>102240</v>
+        <v>91200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,39 +818,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -866,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538473</v>
+        <v>538478</v>
       </c>
       <c r="R3" t="n">
-        <v>6647623</v>
+        <v>6647653</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -902,11 +893,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca 7 cm i diameter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,6 +908,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # vilande på grenarna # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120284986</v>
+        <v>120285251</v>
       </c>
       <c r="B4" t="n">
-        <v>79558</v>
+        <v>102240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,30 +957,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6457</v>
+        <v>223246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -982,10 +997,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538478</v>
+        <v>538473</v>
       </c>
       <c r="R4" t="n">
-        <v>6647653</v>
+        <v>6647623</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1018,6 +1033,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ca 7 cm i diameter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,26 +1053,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>grovt träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Acer platanoides # grovt träd</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 63684-2020 artfynd.xlsx
+++ b/artfynd/A 63684-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120284986</v>
+        <v>120285005</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
+        <v>91200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,25 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -773,22 +781,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>grovt träd</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Acer platanoides # grovt träd</t>
+          <t>Horizontal, dead without ground contact # vilande på grenarna # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120285005</v>
+        <v>120284986</v>
       </c>
       <c r="B3" t="n">
-        <v>91200</v>
+        <v>79558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,33 +830,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # vilande på grenarna # Picea abies</t>
+          <t>Acer platanoides # grovt träd</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 63684-2020 artfynd.xlsx
+++ b/artfynd/A 63684-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120285005</v>
+        <v>120284986</v>
       </c>
       <c r="B2" t="n">
-        <v>91200</v>
+        <v>79558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>6457</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -781,22 +773,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # vilande på grenarna # Picea abies</t>
+          <t>Acer platanoides # grovt träd</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120284986</v>
+        <v>120285005</v>
       </c>
       <c r="B3" t="n">
-        <v>79558</v>
+        <v>91200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,25 +822,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6457</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>skogslönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>grovt träd</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Acer platanoides # grovt träd</t>
+          <t>Horizontal, dead without ground contact # vilande på grenarna # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
